--- a/tasklist/エネルギー喫緊課題.xlsx
+++ b/tasklist/エネルギー喫緊課題.xlsx
@@ -8,6 +8,9 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$1:$J$11</definedName>
+  </definedNames>
   <calcPr/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{D0CA8CA8-9F24-4464-BF8E-62219DCF47F9}"/>
@@ -16,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="85">
   <si>
     <t>課題ID</t>
   </si>
@@ -90,6 +93,12 @@
     <t>#41炉寿命解析</t>
   </si>
   <si>
+    <t>maxima四則演算</t>
+  </si>
+  <si>
+    <t>26.05.02</t>
+  </si>
+  <si>
     <t>E003</t>
   </si>
   <si>
@@ -136,6 +145,9 @@
   </si>
   <si>
     <t>#26テスラ送電</t>
+  </si>
+  <si>
+    <t>26.04.30</t>
   </si>
   <si>
     <t>E005</t>
@@ -295,11 +307,8 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -817,10 +826,10 @@
       <c r="H2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="I2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="J2" s="1" t="s">
         <v>16</v>
       </c>
     </row>
@@ -849,219 +858,231 @@
       <c r="H3" s="1" t="s">
         <v>23</v>
       </c>
+      <c r="I3" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="4" ht="57">
       <c r="A4" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D4" s="1">
         <v>5</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5" ht="42.75">
       <c r="A5" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D5" s="1">
         <v>3</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="6" ht="28.5">
       <c r="A6" s="1" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D6" s="1">
         <v>4</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="7" ht="42.75">
       <c r="A7" s="1" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D7" s="1">
         <v>2</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="8" ht="42.75">
       <c r="A8" s="1" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D8" s="1">
         <v>4</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="9" ht="42.75">
       <c r="A9" s="1" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="D9" s="1">
         <v>5</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
     </row>
     <row r="10" ht="42.75">
       <c r="A10" s="1" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="D10" s="1">
         <v>1</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="11" ht="42.75">
       <c r="A11" s="1" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="D11" s="1">
         <v>5</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
     </row>
   </sheetData>

--- a/tasklist/エネルギー喫緊課題.xlsx
+++ b/tasklist/エネルギー喫緊課題.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="94">
   <si>
     <t>課題ID</t>
   </si>
@@ -274,15 +274,48 @@
   </si>
   <si>
     <t>全連成プロジェクト</t>
+  </si>
+  <si>
+    <t>E011</t>
+  </si>
+  <si>
+    <t>量子エネルギー</t>
+  </si>
+  <si>
+    <t>量子電池(量子充電・放電モデル)</t>
+  </si>
+  <si>
+    <t>中期(5-8年)</t>
+  </si>
+  <si>
+    <t>超高エネルギー密度・超高速充放電</t>
+  </si>
+  <si>
+    <t>量子デコヒーレンス・実用化未確立</t>
+  </si>
+  <si>
+    <t>,#26テスラ送電連動,#41炉寿命解析,maxima,python,26.05.1</t>
+  </si>
+  <si>
+    <t>26.06.25</t>
+  </si>
+  <si>
+    <t>グラフ1の書き方が誤り、1.5を中心に0.5の振れ</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <sz val="11.000000"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11.000000"/>
+      <color indexed="2"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
@@ -307,9 +340,18 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1085,6 +1127,41 @@
         <v>84</v>
       </c>
     </row>
+    <row r="12" ht="99.75">
+      <c r="A12" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="D12" s="1">
+        <v>3</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="K12" s="4" t="s">
+        <v>93</v>
+      </c>
+    </row>
   </sheetData>
   <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.29999999999999999" footer="0.29999999999999999"/>
